--- a/data/vendor-search/results_all_hub.xlsx
+++ b/data/vendor-search/results_all_hub.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +488,11 @@
           <t>cpe:2.3:a:keware_technologies:homeseer:1.4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>homeseer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +528,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_bsb002_firmware:1707040932:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_bsb002:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,6 +568,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,6 +608,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -623,6 +648,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -658,6 +688,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -693,6 +728,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,6 +768,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -763,6 +808,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +848,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -833,6 +888,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,6 +928,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -903,6 +968,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -938,6 +1008,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -973,6 +1048,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1008,6 +1088,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1043,6 +1128,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1078,6 +1168,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1113,6 +1208,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1148,6 +1248,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1183,6 +1288,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1218,6 +1328,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1253,6 +1368,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1288,6 +1408,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1323,6 +1448,11 @@
           <t>cpe:2.3:o:getvera:vera_edge_firmware:1.7.4452:*:*:*:*:*:*:*|cpe:2.3:h:getvera:vera_edge:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vera edge</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1358,6 +1488,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1393,6 +1528,11 @@
           <t>cpe:2.3:a:homeseer:homeseer_hs2:2.5.0.20:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>homeseer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1428,6 +1568,11 @@
           <t>cpe:2.3:a:homeseer:homeseer_hs2:2.5.0.20:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>homeseer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1463,6 +1608,11 @@
           <t>cpe:2.3:a:homeseer:homeseer_hs2:2.5.0.20:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>homeseer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1498,6 +1648,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1533,6 +1688,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1568,6 +1728,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1603,6 +1768,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1638,6 +1808,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1673,6 +1848,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1708,6 +1888,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1743,6 +1928,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1778,6 +1968,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1813,6 +2008,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1848,6 +2048,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1883,6 +2088,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1918,6 +2128,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1953,6 +2168,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1988,6 +2208,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2023,6 +2248,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2058,6 +2288,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2093,6 +2328,11 @@
           <t>cpe:2.3:o:samsung:sth-eth-250_firmware:0.20.17:*:*:*:*:*:*:*|cpe:2.3:h:samsung:sth-eth-250:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>samsung smartthings hub|smartthings hub</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2128,6 +2368,11 @@
           <t>cpe:2.3:o:getvera:vera_edge_firmware:1.7.4452:*:*:*:*:*:*:*|cpe:2.3:h:getvera:vera_edge:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>vera edge</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2163,6 +2408,11 @@
           <t>cpe:2.3:o:homey:homey_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:homey:homey:-:*:*:*:*:*:*:*|cpe:2.3:o:homey:homey_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:homey:homey_pro:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>homey|homey pro|athom homey</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2198,6 +2448,11 @@
           <t>cpe:2.3:o:fibaro:home_center_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_2:-:*:*:*:*:*:*:*|cpe:2.3:o:fibaro:home_center_lite_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_lite:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>fibaro home center</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2233,6 +2488,11 @@
           <t>cpe:2.3:o:fibaro:home_center_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_2:-:*:*:*:*:*:*:*|cpe:2.3:o:fibaro:home_center_lite_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_lite:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>fibaro home center</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2268,6 +2528,11 @@
           <t>cpe:2.3:o:fibaro:home_center_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_2:-:*:*:*:*:*:*:*|cpe:2.3:o:fibaro:home_center_lite_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_lite:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>fibaro home center</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2303,6 +2568,11 @@
           <t>cpe:2.3:o:fibaro:home_center_2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_2:-:*:*:*:*:*:*:*|cpe:2.3:o:fibaro:home_center_lite_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fibaro:home_center_lite:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>fibaro home center</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2338,6 +2608,11 @@
           <t>cpe:2.3:o:homey:homey_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:homey:homey:-:*:*:*:*:*:*:*|cpe:2.3:o:homey:homey_pro_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:homey:homey_pro:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>homey|homey pro|athom homey</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2373,6 +2648,11 @@
           <t>cpe:2.3:a:home-assistant:home-assistant:2022.03:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nabu casa</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2404,6 +2684,11 @@
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>zigbee coordinator</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2435,6 +2720,11 @@
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2466,6 +2756,11 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2497,6 +2792,11 @@
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2528,6 +2828,11 @@
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2559,6 +2864,11 @@
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2590,6 +2900,11 @@
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2625,6 +2940,11 @@
           <t>cpe:2.3:a:favethemes:homey:*:*:*:*:*:wordpress:*:*</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2660,6 +2980,11 @@
           <t>cpe:2.3:a:favethemes:homey:*:*:*:*:*:wordpress:*:*</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2691,6 +3016,11 @@
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2722,6 +3052,11 @@
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2757,6 +3092,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2792,6 +3132,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2827,6 +3172,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2862,6 +3212,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2897,6 +3252,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2932,6 +3292,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2967,6 +3332,11 @@
           <t>cpe:2.3:o:aqara:hub_m2_firmware:4.3.6_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m2:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:hub_m3_firmware:4.3.6_0025:*:*:*:*:*:*:*|cpe:2.3:h:aqara:hub_m3:-:*:*:*:*:*:*:*|cpe:2.3:o:aqara:camera_hub_g3_firmware:4.1.9_0027:*:*:*:*:*:*:*|cpe:2.3:h:aqara:camera_hub_g3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>aqara hub</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2998,6 +3368,11 @@
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3029,6 +3404,11 @@
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3054,6 +3434,11 @@
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>hubitat|hubitat elevation</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3081,6 +3466,11 @@
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>zigbee coordinator</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3116,6 +3506,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3151,6 +3546,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3186,6 +3586,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3221,6 +3626,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3256,6 +3666,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3291,6 +3706,11 @@
           <t>cpe:2.3:a:doditsolutions:airbnb_clone_script:4:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>homey</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3327,6 +3747,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3363,6 +3788,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3399,6 +3829,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3435,6 +3870,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3471,6 +3911,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3507,6 +3952,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3543,6 +3993,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3579,6 +4034,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>philips hue bridge|hue bridge</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3612,6 +4072,11 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ikea:dirigera_firmware:2.866.4:*:*:*:*:*:*:*|cpe:2.3:h:ikea:dirigera:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ikea dirigera|dirigera</t>
         </is>
       </c>
     </row>
